--- a/Analysis/raw data/Survey 1 clean_near complete_16.6.26.xlsx
+++ b/Analysis/raw data/Survey 1 clean_near complete_16.6.26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ranidavis/Desktop/Bats &amp; agriculture/Beneficial Bats - collaborative paper/IBRC paper analysis/IBRC beneficial bats survey response analysis/Analysis/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2C54DE-CE85-5043-9CA2-1A87CF135EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39997E3-F67E-2345-B99A-4020610BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37740" yWindow="-1960" windowWidth="36180" windowHeight="19100" xr2:uid="{A13CC812-5A33-7B48-9C68-0D1EC558A51C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{A13CC812-5A33-7B48-9C68-0D1EC558A51C}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey 1 clean_near complete_16" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="705">
   <si>
     <t>Status</t>
   </si>
@@ -1941,9 +1941,6 @@
     <t>Fiji</t>
   </si>
   <si>
-    <t>Australia &amp; New Zealand</t>
-  </si>
-  <si>
     <t>Peru &amp; Colombia</t>
   </si>
   <si>
@@ -2159,9 +2156,6 @@
   </si>
   <si>
     <t>Multi-region: Jilin province, yunnan province, henan province, shandong provinc &amp; shanxi province</t>
-  </si>
-  <si>
-    <t>Multi-country: Australia &amp;New Zealand</t>
   </si>
   <si>
     <t>Auckland</t>
@@ -4366,22 +4360,22 @@
         <v>584</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>585</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>583</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -4426,7 +4420,7 @@
         <v>14</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>15</v>
@@ -4435,7 +4429,7 @@
         <v>16</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>17</v>
@@ -4444,7 +4438,7 @@
         <v>18</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>19</v>
@@ -4453,7 +4447,7 @@
         <v>20</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>21</v>
@@ -4462,7 +4456,7 @@
         <v>22</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>23</v>
@@ -4471,7 +4465,7 @@
         <v>24</v>
       </c>
       <c r="AL1" s="22" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="22" customHeight="1" x14ac:dyDescent="0.15">
@@ -4479,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C2" s="28">
         <v>1</v>
@@ -4491,16 +4485,16 @@
         <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>253</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>26</v>
@@ -4583,28 +4577,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C3" s="29">
         <v>1</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>49</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>224</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>49</v>
@@ -4675,19 +4669,19 @@
         <v>25</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C4" s="29">
         <v>1</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>438</v>
@@ -4696,7 +4690,7 @@
         <v>438</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>63</v>
@@ -4765,28 +4759,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C5" s="29">
         <v>1</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>73</v>
@@ -4861,28 +4855,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C6" s="29">
         <v>1</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>83</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>84</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>83</v>
@@ -4955,28 +4949,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C7" s="29">
         <v>1</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>94</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>94</v>
@@ -5051,28 +5045,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C8" s="29">
         <v>1</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>107</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>117</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>107</v>
@@ -5147,28 +5141,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C9" s="29">
         <v>2</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>117</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>26</v>
@@ -5247,28 +5241,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C10" s="29">
         <v>1</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>131</v>
@@ -5341,28 +5335,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C11" s="29">
         <v>2</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>141</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>131</v>
@@ -5435,28 +5429,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C12" s="29">
         <v>3</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>146</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>131</v>
@@ -5531,28 +5525,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C13" s="29">
         <v>4</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>224</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>131</v>
@@ -5629,28 +5623,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C14" s="29">
         <v>5</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>158</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>131</v>
@@ -5725,19 +5719,19 @@
         <v>25</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C15" s="29">
         <v>6</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>438</v>
@@ -5746,7 +5740,7 @@
         <v>438</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>131</v>
@@ -5817,19 +5811,19 @@
         <v>25</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C16" s="29">
         <v>7</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>438</v>
@@ -5838,7 +5832,7 @@
         <v>438</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>131</v>
@@ -5913,19 +5907,19 @@
         <v>25</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C17" s="29">
         <v>8</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>438</v>
@@ -5934,7 +5928,7 @@
         <v>438</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>131</v>
@@ -6009,28 +6003,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C18" s="29">
         <v>9</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>458</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>131</v>
@@ -6101,28 +6095,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C19" s="29">
         <v>10</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>189</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>131</v>
@@ -6197,28 +6191,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C20" s="29">
         <v>11</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>194</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>131</v>
@@ -6291,28 +6285,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C21" s="29">
         <v>12</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>201</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>131</v>
@@ -6383,28 +6377,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C22" s="29">
         <v>13</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>203</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>131</v>
@@ -6477,28 +6471,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C23" s="29">
         <v>14</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>207</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>131</v>
@@ -6571,28 +6565,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C24" s="29">
         <v>15</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>213</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>131</v>
@@ -6665,28 +6659,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C25" s="29">
         <v>16</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>216</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>131</v>
@@ -6759,28 +6753,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C26" s="29">
         <v>17</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>189</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>131</v>
@@ -6853,28 +6847,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C27" s="29">
         <v>18</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>224</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>131</v>
@@ -6943,28 +6937,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C28" s="29">
         <v>19</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>253</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>131</v>
@@ -7035,28 +7029,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C29" s="29">
         <v>20</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>158</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>131</v>
@@ -7129,28 +7123,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C30" s="29">
         <v>21</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>237</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>131</v>
@@ -7223,28 +7217,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C31" s="29">
         <v>1</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>241</v>
@@ -7323,28 +7317,28 @@
         <v>25</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C32" s="29">
         <v>2</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>253</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>26</v>
@@ -7423,28 +7417,28 @@
         <v>25</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C33" s="29">
         <v>1</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>264</v>
@@ -7517,7 +7511,7 @@
         <v>25</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C34" s="29">
         <v>1</v>
@@ -7529,16 +7523,16 @@
         <v>273</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>273</v>
@@ -7609,28 +7603,28 @@
         <v>25</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C35" s="29">
         <v>1</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>281</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>224</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>281</v>
@@ -7665,7 +7659,7 @@
         <v>69</v>
       </c>
       <c r="V35" s="23" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="W35" s="23"/>
       <c r="X35" s="12" t="s">
@@ -7699,28 +7693,28 @@
         <v>25</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C36" s="29">
         <v>1</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>286</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>286</v>
@@ -7797,28 +7791,28 @@
         <v>25</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C37" s="29">
         <v>2</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>286</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>286</v>
@@ -7887,28 +7881,28 @@
         <v>25</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C38" s="29">
         <v>1</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>302</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>117</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>302</v>
@@ -7987,28 +7981,28 @@
         <v>25</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C39" s="29">
         <v>2</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>302</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>314</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>302</v>
@@ -8085,28 +8079,28 @@
         <v>25</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C40" s="28">
         <v>1</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>443</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>324</v>
@@ -8179,28 +8173,28 @@
         <v>25</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C41" s="28">
         <v>2</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>443</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>324</v>
@@ -8279,28 +8273,28 @@
         <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C42" s="28">
         <v>3</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>443</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>324</v>
@@ -8377,28 +8371,28 @@
         <v>25</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C43" s="28">
         <v>1</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>341</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J43" s="14" t="s">
         <v>341</v>
@@ -8479,28 +8473,28 @@
         <v>25</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C44" s="28">
         <v>2</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>341</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J44" s="14" t="s">
         <v>341</v>
@@ -8581,28 +8575,28 @@
         <v>25</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C45" s="28">
         <v>3</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>341</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>224</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J45" s="14" t="s">
         <v>341</v>
@@ -8671,28 +8665,28 @@
         <v>25</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C46" s="28">
         <v>1</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>94</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>158</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>94</v>
@@ -8771,28 +8765,28 @@
         <v>25</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C47" s="28">
         <v>2</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>94</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>94</v>
@@ -8871,28 +8865,28 @@
         <v>25</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C48" s="29">
         <v>1</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>158</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>73</v>
@@ -8963,28 +8957,28 @@
         <v>25</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C49" s="29">
         <v>2</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>398</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>73</v>
@@ -9053,7 +9047,7 @@
         <v>25</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C50" s="28">
         <v>1</v>
@@ -9065,7 +9059,7 @@
         <v>404</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>438</v>
@@ -9074,7 +9068,7 @@
         <v>438</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>404</v>
@@ -9145,28 +9139,28 @@
         <v>25</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C51" s="28">
         <v>2</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>404</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>404</v>
@@ -9235,28 +9229,28 @@
         <v>25</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C52" s="29">
         <v>1</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>549</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>224</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>418</v>
@@ -9321,28 +9315,28 @@
         <v>25</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C53" s="29">
         <v>1</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>422</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>422</v>
@@ -9417,7 +9411,7 @@
         <v>25</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C54" s="29">
         <v>1</v>
@@ -9429,16 +9423,16 @@
         <v>341</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>341</v>
@@ -9507,19 +9501,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C55" s="29">
         <v>2</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>341</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>438</v>
@@ -9528,7 +9522,7 @@
         <v>438</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>341</v>
@@ -9595,7 +9589,7 @@
         <v>25</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C56" s="29">
         <v>3</v>
@@ -9607,16 +9601,16 @@
         <v>443</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>443</v>
@@ -9689,28 +9683,28 @@
         <v>25</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C57" s="29">
         <v>1</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>452</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>117</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>452</v>
@@ -9781,7 +9775,7 @@
         <v>582</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C58" s="28">
         <v>1</v>
@@ -9793,16 +9787,16 @@
         <v>404</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>458</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>404</v>
@@ -9865,7 +9859,7 @@
         <v>25</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C59" s="28">
         <v>1</v>
@@ -9877,16 +9871,16 @@
         <v>281</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>458</v>
       </c>
       <c r="H59" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>281</v>
@@ -9953,28 +9947,28 @@
         <v>25</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C60" s="28">
         <v>2</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>281</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>281</v>
@@ -10043,28 +10037,28 @@
         <v>25</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C61" s="29">
         <v>1</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>241</v>
@@ -10129,28 +10123,28 @@
         <v>25</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C62" s="29">
         <v>1</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>73</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>158</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>73</v>
@@ -10217,28 +10211,28 @@
         <v>25</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C63" s="29">
         <v>1</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>241</v>
@@ -10319,28 +10313,28 @@
         <v>25</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C64" s="29">
         <v>1</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>49</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>49</v>
@@ -10411,28 +10405,28 @@
         <v>25</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C65" s="29">
         <v>1</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>73</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>495</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>73</v>
@@ -10509,19 +10503,19 @@
         <v>25</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C66" s="28">
         <v>1</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>505</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>438</v>
@@ -10530,7 +10524,7 @@
         <v>438</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>505</v>
@@ -10611,7 +10605,7 @@
         <v>25</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C67" s="29">
         <v>1</v>
@@ -10623,16 +10617,16 @@
         <v>586</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>518</v>
@@ -10715,28 +10709,28 @@
         <v>25</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C68" s="29">
         <v>1</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>587</v>
+        <v>73</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>532</v>
@@ -10803,7 +10797,7 @@
         <v>25</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C69" s="29">
         <v>1</v>
@@ -10815,16 +10809,16 @@
         <v>538</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>538</v>
@@ -10889,7 +10883,7 @@
         <v>25</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C70" s="29">
         <v>2</v>
@@ -10901,16 +10895,16 @@
         <v>542</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>542</v>
@@ -10975,7 +10969,7 @@
         <v>25</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C71" s="29">
         <v>3</v>
@@ -10987,16 +10981,16 @@
         <v>49</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>495</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>49</v>
@@ -11061,28 +11055,28 @@
         <v>25</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C72" s="29">
         <v>1</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>549</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>549</v>
@@ -11149,7 +11143,7 @@
         <v>25</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C73" s="28">
         <v>1</v>
@@ -11161,16 +11155,16 @@
         <v>26</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>458</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>26</v>
@@ -11207,7 +11201,7 @@
         <v>37</v>
       </c>
       <c r="V73" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="W73" s="6"/>
       <c r="X73" s="6" t="s">
@@ -11247,7 +11241,7 @@
         <v>25</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C74" s="28">
         <v>2</v>
@@ -11259,16 +11253,16 @@
         <v>26</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>117</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>26</v>
@@ -11303,7 +11297,7 @@
         <v>37</v>
       </c>
       <c r="V74" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="W74" s="6"/>
       <c r="X74" s="6" t="s">
@@ -11336,7 +11330,7 @@
         <v>411</v>
       </c>
       <c r="AK74" s="8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AL74" s="6"/>
     </row>
@@ -11345,7 +11339,7 @@
         <v>25</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C75" s="28">
         <v>3</v>
@@ -11357,7 +11351,7 @@
         <v>26</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>438</v>
@@ -11366,7 +11360,7 @@
         <v>438</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>26</v>
@@ -11401,7 +11395,7 @@
         <v>69</v>
       </c>
       <c r="V75" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="W75" s="6"/>
       <c r="X75" s="6" t="s">
@@ -11443,19 +11437,19 @@
         <v>25</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C76" s="29">
         <v>1</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>73</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G76" s="11" t="s">
         <v>438</v>
@@ -11464,7 +11458,7 @@
         <v>438</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>73</v>
@@ -11541,7 +11535,7 @@
         <v>582</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C77" s="30"/>
       <c r="D77" s="18"/>
@@ -11550,7 +11544,7 @@
       <c r="G77" s="18"/>
       <c r="H77" s="18"/>
       <c r="I77" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="J77" s="18"/>
       <c r="K77" s="18"/>
@@ -11587,7 +11581,7 @@
         <v>582</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C78" s="30"/>
       <c r="D78" s="18"/>
@@ -11596,7 +11590,7 @@
       <c r="G78" s="18"/>
       <c r="H78" s="18"/>
       <c r="I78" s="18" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="J78" s="18"/>
       <c r="K78" s="18"/>
@@ -11633,7 +11627,7 @@
         <v>582</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C79" s="30"/>
       <c r="D79" s="18"/>
@@ -11642,7 +11636,7 @@
       <c r="G79" s="18"/>
       <c r="H79" s="18"/>
       <c r="I79" s="18" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J79" s="18"/>
       <c r="K79" s="18"/>
@@ -11679,7 +11673,7 @@
         <v>582</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C80" s="30"/>
       <c r="D80" s="18"/>
@@ -11688,7 +11682,7 @@
       <c r="G80" s="18"/>
       <c r="H80" s="18"/>
       <c r="I80" s="19" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="J80" s="18"/>
       <c r="K80" s="18"/>
@@ -11725,7 +11719,7 @@
         <v>582</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C81" s="30"/>
       <c r="D81" s="18"/>
@@ -11734,7 +11728,7 @@
       <c r="G81" s="18"/>
       <c r="H81" s="18"/>
       <c r="I81" s="19" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="J81" s="18"/>
       <c r="K81" s="18"/>
